--- a/backend/data/financials_by_company/0092.HK.xlsx
+++ b/backend/data/financials_by_company/0092.HK.xlsx
@@ -3674,187 +3674,187 @@
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>marketState</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="EK1" t="inlineStr">
@@ -3947,28 +3947,28 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>0.182</v>
+        <v>0.184</v>
       </c>
       <c r="T2" t="n">
-        <v>0.182</v>
+        <v>0.186</v>
       </c>
       <c r="U2" t="n">
-        <v>0.182</v>
+        <v>0.185</v>
       </c>
       <c r="V2" t="n">
-        <v>0.188</v>
+        <v>0.186</v>
       </c>
       <c r="W2" t="n">
-        <v>0.182</v>
+        <v>0.184</v>
       </c>
       <c r="X2" t="n">
-        <v>0.182</v>
+        <v>0.186</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.182</v>
+        <v>0.185</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.188</v>
+        <v>0.186</v>
       </c>
       <c r="AA2" t="n">
         <v>1394755200</v>
@@ -3980,28 +3980,28 @@
         <v>2.81</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.532</v>
+        <v>-0.533</v>
       </c>
       <c r="AE2" t="n">
-        <v>24000</v>
+        <v>265</v>
       </c>
       <c r="AF2" t="n">
-        <v>24000</v>
+        <v>265</v>
       </c>
       <c r="AG2" t="n">
-        <v>365717</v>
+        <v>335586</v>
       </c>
       <c r="AH2" t="n">
-        <v>223880</v>
+        <v>95908</v>
       </c>
       <c r="AI2" t="n">
-        <v>223880</v>
+        <v>95908</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.162</v>
+        <v>0.176</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.188</v>
+        <v>0.185</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -4010,10 +4010,10 @@
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>206351584</v>
+        <v>201961136</v>
       </c>
       <c r="AO2" t="n">
-        <v>206351591</v>
+        <v>203058746</v>
       </c>
       <c r="AP2" t="n">
         <v>0.138</v>
@@ -4028,13 +4028,13 @@
         <v>0.1</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.9831233</v>
+        <v>2.9196527</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.188</v>
+        <v>0.18756</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.19336</v>
+        <v>0.19384</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -4051,7 +4051,7 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>154207920</v>
+        <v>150269088</v>
       </c>
       <c r="BB2" t="n">
         <v>-0.72940004</v>
@@ -4075,7 +4075,7 @@
         <v>0.089</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.1123595</v>
+        <v>2.0674157</v>
       </c>
       <c r="BJ2" t="n">
         <v>1751241600</v>
@@ -4101,16 +4101,16 @@
         <v>1710806400</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.229</v>
+        <v>2.172</v>
       </c>
       <c r="BR2" t="n">
-        <v>-1.769</v>
+        <v>-1.724</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0.035897434</v>
+        <v>-0.07070708000000001</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="BU2" t="n">
         <v>0.133697</v>
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="BX2" t="n">
-        <v>0.188</v>
+        <v>0.184</v>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
@@ -4223,140 +4223,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="CZ2" t="n">
+        <v>-0.0035600066</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>-0.018980628</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>-0.009839997</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>-0.0507635</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DG2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DA2" t="n">
-        <v>1781682474</v>
-      </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DH2" t="n">
+        <v>1782957744</v>
+      </c>
+      <c r="DI2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>finmb_878108</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DF2" t="n">
+      <c r="DM2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="DR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1022031000000</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>0.185 - 0.186</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DW2" t="n">
+        <v>335586</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>0.046000004</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0.33333337</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>0.138 - 0.28</t>
+        </is>
+      </c>
+      <c r="EA2" t="n">
+        <v>-0.096</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-0.34285715</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>-7.0707083</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>1740667719</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>1740667719</v>
+      </c>
+      <c r="EF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="EH2" t="inlineStr">
         <is>
           <t>CHAMPION TECH</t>
         </is>
       </c>
-      <c r="DK2" t="n">
-        <v>3.296702</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="DM2" t="inlineStr">
+      <c r="EI2" t="inlineStr">
         <is>
           <t>Champion Technology Holdings Limited</t>
         </is>
       </c>
-      <c r="DN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>1022031000000</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0.0059999973</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>0.182 - 0.188</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DS2" t="n">
-        <v>365717</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.049999997</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0.3623188</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>0.138 - 0.28</t>
-        </is>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.09200000999999999</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.32857147</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-3.5897434</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1740667719</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>1740667719</v>
-      </c>
-      <c r="EB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-0.0053600073</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.027720353</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EJ2" t="b">
-        <v>0</v>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
       </c>
       <c r="EK2" t="inlineStr"/>
     </row>
